--- a/Data/Input/TransaccionesSAP - copia.xlsx
+++ b/Data/Input/TransaccionesSAP - copia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C25D95-0AD9-4AB1-9DB9-2A132E63C7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5A05C-60BD-4EC1-A074-DCA3DDA413D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1980" windowWidth="21600" windowHeight="11295" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
   <sheets>
     <sheet name="TransaccionesSAP" sheetId="1" r:id="rId1"/>
@@ -73,25 +73,25 @@
     <t>ZSD053</t>
   </si>
   <si>
+    <t>LT23</t>
+  </si>
+  <si>
+    <t>VL06O</t>
+  </si>
+  <si>
+    <t>listas sal</t>
+  </si>
+  <si>
+    <t>vista posicion</t>
+  </si>
+  <si>
+    <t>ODM</t>
+  </si>
+  <si>
+    <t>Step4</t>
+  </si>
+  <si>
     <t>filtrar pedido</t>
-  </si>
-  <si>
-    <t>LT23</t>
-  </si>
-  <si>
-    <t>VL06O</t>
-  </si>
-  <si>
-    <t>listas sal</t>
-  </si>
-  <si>
-    <t>vista posicion</t>
-  </si>
-  <si>
-    <t>ODM</t>
-  </si>
-  <si>
-    <t>Step4</t>
   </si>
 </sst>
 </file>
@@ -955,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,7 +1040,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
         <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -1074,12 +1074,12 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
